--- a/artfynd/A 56840-2023 artfynd.xlsx
+++ b/artfynd/A 56840-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 56840-2023 artfynd.xlsx
+++ b/artfynd/A 56840-2023 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>17225874</v>
+        <v>17225871</v>
       </c>
       <c r="B2" t="n">
-        <v>89406</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89292</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1204</v>
+        <v>510</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>550537.6824804267</v>
+        <v>550578</v>
       </c>
       <c r="R2" t="n">
-        <v>7240721.252424958</v>
+        <v>7240791</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +743,9 @@
           <t>2014-10-02</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2014-10-02</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -809,37 +794,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>17225878</v>
+        <v>17225865</v>
       </c>
       <c r="B3" t="n">
-        <v>90160</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>918</v>
+        <v>658</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tajgaskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Laurilia sulcata</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Burt) Pouzar</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -849,10 +829,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>550497.1985529071</v>
+        <v>550575</v>
       </c>
       <c r="R3" t="n">
-        <v>7240759.911864709</v>
+        <v>7240913</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -882,19 +862,9 @@
           <t>2014-10-02</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2014-10-02</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -943,15 +913,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>17225880</v>
+        <v>17225867</v>
       </c>
       <c r="B4" t="n">
-        <v>89406</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -959,21 +924,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1204</v>
+        <v>658</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -983,10 +948,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>550428.8847880196</v>
+        <v>550562</v>
       </c>
       <c r="R4" t="n">
-        <v>7240783.859766008</v>
+        <v>7240871</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1016,19 +981,9 @@
           <t>2014-10-02</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2014-10-02</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1077,15 +1032,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>17225881</v>
+        <v>17225872</v>
       </c>
       <c r="B5" t="n">
-        <v>90160</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92721</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1117,10 +1067,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>550396.5111937881</v>
+        <v>550585</v>
       </c>
       <c r="R5" t="n">
-        <v>7240838.567508022</v>
+        <v>7240783</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1150,19 +1100,9 @@
           <t>2014-10-02</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2014-10-02</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1211,15 +1151,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>17225879</v>
+        <v>17225873</v>
       </c>
       <c r="B6" t="n">
-        <v>90160</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92721</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1251,10 +1186,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>550428.8847880196</v>
+        <v>550568</v>
       </c>
       <c r="R6" t="n">
-        <v>7240783.859766008</v>
+        <v>7240715</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1284,19 +1219,9 @@
           <t>2014-10-02</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2014-10-02</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1345,37 +1270,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>17225877</v>
+        <v>17225878</v>
       </c>
       <c r="B7" t="n">
-        <v>89388</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92721</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1108</v>
+        <v>918</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tajgaskinn</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Laurilia sulcata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Burt) Pouzar</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1385,10 +1305,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>550470.9600357043</v>
+        <v>550497</v>
       </c>
       <c r="R7" t="n">
-        <v>7240774.533444141</v>
+        <v>7240760</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1418,19 +1338,9 @@
           <t>2014-10-02</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2014-10-02</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1479,37 +1389,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>17225876</v>
+        <v>17225879</v>
       </c>
       <c r="B8" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92721</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>918</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tajgaskinn</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Laurilia sulcata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Burt) Pouzar</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1519,10 +1424,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>550508.883807609</v>
+        <v>550429</v>
       </c>
       <c r="R8" t="n">
-        <v>7240714.059166458</v>
+        <v>7240784</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1552,19 +1457,9 @@
           <t>2014-10-02</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2014-10-02</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1613,37 +1508,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>17225864</v>
+        <v>17225881</v>
       </c>
       <c r="B9" t="n">
-        <v>89406</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92721</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1204</v>
+        <v>918</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Tajgaskinn</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Laurilia sulcata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Burt) Pouzar</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1653,10 +1543,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>550575.4671700419</v>
+        <v>550397</v>
       </c>
       <c r="R9" t="n">
-        <v>7240912.808510466</v>
+        <v>7240839</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1686,19 +1576,9 @@
           <t>2014-10-02</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2014-10-02</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1750,12 +1630,7 @@
         <v>17225869</v>
       </c>
       <c r="B10" t="n">
-        <v>89388</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1787,10 +1662,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>550532.0440620567</v>
+        <v>550532</v>
       </c>
       <c r="R10" t="n">
-        <v>7240854.289203924</v>
+        <v>7240854</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1820,19 +1695,9 @@
           <t>2014-10-02</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2014-10-02</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1881,37 +1746,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>17225872</v>
+        <v>17225877</v>
       </c>
       <c r="B11" t="n">
-        <v>90160</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>918</v>
+        <v>1108</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tajgaskinn</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Laurilia sulcata</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Burt) Pouzar</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1921,10 +1781,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>550584.8211945856</v>
+        <v>550471</v>
       </c>
       <c r="R11" t="n">
-        <v>7240783.187549875</v>
+        <v>7240775</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1954,19 +1814,9 @@
           <t>2014-10-02</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2014-10-02</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -2015,37 +1865,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>17225865</v>
+        <v>17225864</v>
       </c>
       <c r="B12" t="n">
-        <v>89673</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>658</v>
+        <v>1204</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -2055,10 +1900,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>550575.4671700419</v>
+        <v>550575</v>
       </c>
       <c r="R12" t="n">
-        <v>7240912.808510466</v>
+        <v>7240913</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2088,19 +1933,9 @@
           <t>2014-10-02</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2014-10-02</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2149,37 +1984,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>17225867</v>
+        <v>17225874</v>
       </c>
       <c r="B13" t="n">
-        <v>89673</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>658</v>
+        <v>1204</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2189,10 +2019,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>550561.9401086449</v>
+        <v>550538</v>
       </c>
       <c r="R13" t="n">
-        <v>7240870.711523177</v>
+        <v>7240721</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2222,19 +2052,9 @@
           <t>2014-10-02</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2014-10-02</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2283,53 +2103,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>17225866</v>
+        <v>17225875</v>
       </c>
       <c r="B14" t="n">
-        <v>76862</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6443</v>
+        <v>1204</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Sotlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Acolium inquinans</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Sm.) A.Massal.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Sörliden, på låg höjd i västsluttningen, Ås lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>550588.3197681399</v>
+        <v>550506</v>
       </c>
       <c r="R14" t="n">
-        <v>7240920.983681189</v>
+        <v>7240689</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2359,33 +2171,17 @@
           <t>2014-10-02</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2014-10-02</t>
         </is>
       </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Artbestämd av Anders Nordin</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2405,11 +2201,6 @@
       <c r="AO14" t="inlineStr">
         <is>
           <t>1 substratenheter # Picea abies</t>
-        </is>
-      </c>
-      <c r="AS14" t="inlineStr">
-        <is>
-          <t>Anders Nordin</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2431,15 +2222,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>17225870</v>
+        <v>17225880</v>
       </c>
       <c r="B15" t="n">
-        <v>89745</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2447,36 +2233,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1505</v>
+        <v>1204</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kristallticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Skeletocutis stellae</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Pilát) Jean Keller</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Sörliden, på låg höjd i västsluttningen, Ås lm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>550532.0440620567</v>
+        <v>550429</v>
       </c>
       <c r="R15" t="n">
-        <v>7240854.289203924</v>
+        <v>7240784</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2506,31 +2290,16 @@
           <t>2014-10-02</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2014-10-02</t>
         </is>
       </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
-      </c>
-      <c r="AF15" t="inlineStr">
-        <is>
-          <t>mikroskoperad</t>
-        </is>
       </c>
       <c r="AG15" t="b">
         <v>0</v>
@@ -2572,15 +2341,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>17225871</v>
+        <v>17225863</v>
       </c>
       <c r="B16" t="n">
-        <v>85703</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2588,21 +2352,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>510</v>
+        <v>1312</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A. Curtis.) Pouzar</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2612,10 +2376,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>550577.9800103355</v>
+        <v>550557</v>
       </c>
       <c r="R16" t="n">
-        <v>7240791.024461026</v>
+        <v>7240881</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2645,19 +2409,9 @@
           <t>2014-10-02</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2014-10-02</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2706,50 +2460,47 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>17225868</v>
+        <v>17225870</v>
       </c>
       <c r="B17" t="n">
-        <v>78570</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92295</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2081</v>
+        <v>1505</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Kristallticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Skeletocutis stellae</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Pilát) Jean Keller</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Sörliden, på låg höjd i västsluttningen, Ås lm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>550544.4329127604</v>
+        <v>550532</v>
       </c>
       <c r="R17" t="n">
-        <v>7240840.686553909</v>
+        <v>7240854</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2779,38 +2530,33 @@
           <t>2014-10-02</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2014-10-02</t>
         </is>
       </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr">
+        <is>
+          <t>mikroskoperad</t>
+        </is>
+      </c>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AN17" t="n">
@@ -2818,7 +2564,7 @@
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>1 substratenheter # Salix caprea</t>
+          <t>1 substratenheter # Picea abies</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2840,37 +2586,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>17225873</v>
+        <v>17225868</v>
       </c>
       <c r="B18" t="n">
-        <v>90160</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>918</v>
+        <v>2081</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tajgaskinn</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Laurilia sulcata</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Burt) Pouzar</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2880,10 +2621,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>550567.9755293828</v>
+        <v>550544</v>
       </c>
       <c r="R18" t="n">
-        <v>7240714.65556793</v>
+        <v>7240841</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2913,21 +2654,11 @@
           <t>2014-10-02</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2014-10-02</t>
         </is>
       </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
@@ -2939,12 +2670,12 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AN18" t="n">
@@ -2952,7 +2683,7 @@
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>1 substratenheter # Picea abies</t>
+          <t>1 substratenheter # Salix caprea</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2974,50 +2705,48 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>17225863</v>
+        <v>17225866</v>
       </c>
       <c r="B19" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78685</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1312</v>
+        <v>6443</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Sotlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Acolium inquinans</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Sm.) A.Massal.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Sörliden, på låg höjd i västsluttningen, Ås lm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>550556.7392862749</v>
+        <v>550588</v>
       </c>
       <c r="R19" t="n">
-        <v>7240880.669666152</v>
+        <v>7240921</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -3047,19 +2776,14 @@
           <t>2014-10-02</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2014-10-02</t>
         </is>
       </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Artbestämd av Anders Nordin</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3068,6 +2792,7 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -3087,6 +2812,11 @@
       <c r="AO19" t="inlineStr">
         <is>
           <t>1 substratenheter # Picea abies</t>
+        </is>
+      </c>
+      <c r="AS19" t="inlineStr">
+        <is>
+          <t>Anders Nordin</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
